--- a/SuppTable1.xlsx
+++ b/SuppTable1.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/englar/Documents/Banchereau_Lab/Paper_Writing/Long Read RNA Sequencing Identifies Intron Retention as a Major Regulator of STAT2 Function in Lung Adenocarcinoma/SCIENCE/Revisions1/Supplementary Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/englar/Documents/Banchereau_Lab/Paper_Writing/Long Read RNA Sequencing Identifies Intron Retention as a Major Regulator of STAT2 Function in Lung Adenocarcinoma/SCIENCE/Revisions2/Supplementary Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B487ED5B-63C4-194A-83C9-A19EBFB9001E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA7B995-48E1-3B4C-B310-6239FE7B75EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="760" windowWidth="26640" windowHeight="17500" activeTab="4" xr2:uid="{00A0855B-EE9D-114F-93B7-9F733089314B}"/>
+    <workbookView xWindow="2520" yWindow="760" windowWidth="26640" windowHeight="17500" xr2:uid="{00A0855B-EE9D-114F-93B7-9F733089314B}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="5" r:id="rId1"/>
     <sheet name="Table S1A" sheetId="2" r:id="rId2"/>
     <sheet name="Table S1B" sheetId="3" r:id="rId3"/>
     <sheet name="Table S1C" sheetId="4" r:id="rId4"/>
-    <sheet name="Table S1D" sheetId="6" r:id="rId5"/>
+    <sheet name="Table S1D" sheetId="7" r:id="rId5"/>
+    <sheet name="Table S1E" sheetId="8" r:id="rId6"/>
+    <sheet name="Table S1F" sheetId="9" r:id="rId7"/>
+    <sheet name="Table S1G" sheetId="10" r:id="rId8"/>
+    <sheet name="Table S1H" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="130">
   <si>
     <t>Classification</t>
   </si>
@@ -375,31 +379,6 @@
     <t>Putative truncated isoform; all splice junctions in the isoform are found in a closest matching reference isoform, but some of the splice junctions in the reference isoform are missing</t>
   </si>
   <si>
-    <t xml:space="preserve">• (Reverse transcription artifact flag FALSE) AND
-• (Bite junction artifact flag FALSE) AND
-• ( (Isoform termination site within 99 bp of a reference-annotated gene termination site) OR (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) AND
-• ( (Minimum SR-seq coverage of 10 reads at all splice junctions) OR (Isoform is mono-exonic) ) </t>
-  </si>
-  <si>
-    <t>• (Reverse transcription artifact flag FALSE) AND
-• (Bite junction artifact flag FALSE) AND
-• (Minimum SR-seq coverage of 10 reads at all splice junctions) AND
-• ( (Isoform start site within 99 bp of a reference-annotated gene start site) OR (Isoform start site within 99 bp of an annotated CAGE peak) ) AND
-• ( (Isoform termination site within 99 bp of a reference-annotated gene termination site) OR ( (PolyA motif found at isoform termination site) AND (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) )</t>
-  </si>
-  <si>
-    <t>• (Reverse transcription artifact flag FALSE) AND
-• (Bite junction artifact flag FALSE) AND
-• ( (Isoform termination site within 99 bp of a reference-annotated gene termination site) OR (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) AND
-• ( ( (Minimum SR-seq coverage of 10 reads at all splice junctions) AND (All splice junctions are canonical) ) OR ( (Minimum SR-seq coverage of 50 reads at all splice junctions) AND (Non-canonical splice junctions are present) ) OR ( (Isoform is mono-exonic) AND (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) )</t>
-  </si>
-  <si>
-    <t>• (Reverse transcription artifact flag FALSE) AND
-• (Bite junction artifact flag FALSE) AND
-• ( (Isoform termination site within 99 bp of a reference-annotated gene termination site) OR (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) AND
-• ( ( (Minimum SR-seq coverage of 10 reads at all splice junctions) AND (All splice junctions are canonical) ) OR ( (Minimum SR-seq coverage of 50 reads at all splice junctions) AND (Non-canonical splice junctions are present) ) )</t>
-  </si>
-  <si>
     <t>Isoform contains a at least one novel splice junction composed of a novel combination of known splice sites</t>
   </si>
   <si>
@@ -409,14 +388,128 @@
     <t>All other isoform categories (intergenic isoforms, fusion isoforms, antisense isoforms, etc.)</t>
   </si>
   <si>
+    <t>Table S1A. Clinical characteristics of patients selected for LR-seq</t>
+  </si>
+  <si>
+    <t>Table S1B. LR-seq library summary statistics</t>
+  </si>
+  <si>
+    <t>Table S1C. LR-seq library number of reads by mean Phread score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• (Reverse transcription artifact flag FALSE) AND
+• (Bite junction artifact flag FALSE) AND
+• ( (Isoform termination site within 25 bp of a reference-annotated gene termination site) OR (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) AND
+• ( (Minimum SR-seq coverage of 10 reads at all splice junctions) OR (Isoform is mono-exonic) ) </t>
+  </si>
+  <si>
     <t>• (Reverse transcription artifact flag FALSE) AND
 • (Bite junction artifact flag FALSE) AND
+• (Minimum SR-seq coverage of 10 reads at all splice junctions) AND
+• ( (Isoform start site within 25 bp of a reference-annotated gene start site) OR (Isoform start site within an annotated CAGE peak) ) AND
+• ( (Isoform termination site within 25 bp of a reference-annotated gene termination site) OR ( (PolyA motif found within 25 nucleotides upstream of isoform termination site) AND (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) )</t>
+  </si>
+  <si>
+    <t>• (Reverse transcription artifact flag FALSE) AND
+• (Bite junction artifact flag FALSE) AND
+• ( (Isoform termination site within 25 bp of a reference-annotated gene termination site) OR (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) AND
+• ( ( (Minimum SR-seq coverage of 10 reads at all splice junctions) AND (All splice junctions are canonical) ) OR ( (Minimum SR-seq coverage of 50 reads at all splice junctions) AND (Non-canonical splice junctions are present) ) OR ( (Isoform is mono-exonic) AND (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) )</t>
+  </si>
+  <si>
+    <t>• (Reverse transcription artifact flag FALSE) AND
+• (Bite junction artifact flag FALSE) AND
+• ( (Isoform termination site within 25 bp of a reference-annotated gene termination site) OR (Internal priming artifact flag perc_A_downstream_TTS FALSE) ) AND
+• ( ( (Minimum SR-seq coverage of 10 reads at all splice junctions) AND (All splice junctions are canonical) ) OR ( (Minimum SR-seq coverage of 50 reads at all splice junctions) AND (Non-canonical splice junctions are present) ) )</t>
+  </si>
+  <si>
+    <t>• (Reverse transcription artifact flag FALSE) AND
 • (Internal priming artifact flag perc_A_downstream_TTS FALSE) AND
-• ( (Minimum SR-seq coverage of 10 reads at all splice junctions) AND (All splice junctions are canonical) )</t>
+• (  (Bite junction artifact flag FALSE) AND (Minimum SR-seq coverage of 10 reads at all splice junctions) AND (All splice junctions are canonical) ) OR ( Isoform is mono-exonic)</t>
+  </si>
+  <si>
+    <t>TSS tolerance (bp)</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>FSM</t>
+  </si>
+  <si>
+    <t>ISM</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>NNC</t>
+  </si>
+  <si>
+    <t>Table S1E. Effect of TTS stringency on isoform filtering</t>
+  </si>
+  <si>
+    <t>TTS tolerance (bp)</t>
+  </si>
+  <si>
+    <t>CAGE tolerance (bp)</t>
+  </si>
+  <si>
+    <t>PolyA tolerance (bp)</t>
+  </si>
+  <si>
+    <t>Table S1H. Filtering parameters for LR-seq isoforms by SQANTI3 structural category</t>
+  </si>
+  <si>
+    <t>Table S1D. Effect of TSS stringency on isoform filtering</t>
+  </si>
+  <si>
+    <t>Table S1G. Effect of polyA distance stringency on isoform filtering</t>
   </si>
   <si>
     <r>
-      <t>Table S1D</t>
+      <t xml:space="preserve">Table S1D. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Effect of TSS stringency on isoform filtering</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table S1E. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Effect of TTS stringency on isoform filtering</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table S1G. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Effect of polyA distance stringency on isoform filtering</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Table S1H</t>
     </r>
     <r>
       <rPr>
@@ -429,23 +522,28 @@
     </r>
   </si>
   <si>
-    <t>Table S1A. Clinical characteristics of patients selected for LR-seq</t>
+    <t>Table S1F. Effect of CAGE peak stringency on isoform filtering</t>
   </si>
   <si>
-    <t>Table S1B. LR-seq library summary statistics</t>
-  </si>
-  <si>
-    <t>Table S1C. LR-seq library number of reads by mean Phread score</t>
-  </si>
-  <si>
-    <t>Table S1D. Filtering parameters for LR-seq isoforms by SQANTI3 structural category</t>
+    <r>
+      <t xml:space="preserve">Table S1F. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Effect of CAGE peak stringency on isoform filtering</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -494,6 +592,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -551,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -584,6 +688,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210D5787-0458-2444-9F0B-6BC040E78D11}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -945,8 +1050,28 @@
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="13" t="s">
-        <v>108</v>
+      <c r="A6" s="18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +1098,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1455,7 +1580,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="9" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1776,7 +1901,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4611,6 +4736,8257 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36363CDF-9E9B-C849-A973-2A7CFF142786}">
+  <dimension ref="A1:G103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>99</v>
+      </c>
+      <c r="B4" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D4" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E4" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>98</v>
+      </c>
+      <c r="B5" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C5" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20842</v>
+      </c>
+      <c r="E5" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>97</v>
+      </c>
+      <c r="B6" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C6" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20796</v>
+      </c>
+      <c r="E6" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>96</v>
+      </c>
+      <c r="B7" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C7" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D7" s="2">
+        <v>20746</v>
+      </c>
+      <c r="E7" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>95</v>
+      </c>
+      <c r="B8" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C8" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D8" s="2">
+        <v>20701</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>94</v>
+      </c>
+      <c r="B9" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20665</v>
+      </c>
+      <c r="E9" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G9" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>93</v>
+      </c>
+      <c r="B10" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20606</v>
+      </c>
+      <c r="E10" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F10" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G10" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>92</v>
+      </c>
+      <c r="B11" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20552</v>
+      </c>
+      <c r="E11" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G11" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D12" s="2">
+        <v>20521</v>
+      </c>
+      <c r="E12" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G12" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
+        <v>90</v>
+      </c>
+      <c r="B13" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C13" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20478</v>
+      </c>
+      <c r="E13" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G13" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>89</v>
+      </c>
+      <c r="B14" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D14" s="2">
+        <v>20432</v>
+      </c>
+      <c r="E14" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F14" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G14" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
+        <v>88</v>
+      </c>
+      <c r="B15" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C15" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20386</v>
+      </c>
+      <c r="E15" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F15" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G15" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C16" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D16" s="2">
+        <v>20335</v>
+      </c>
+      <c r="E16" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F16" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G16" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2">
+        <v>86</v>
+      </c>
+      <c r="B17" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D17" s="2">
+        <v>20280</v>
+      </c>
+      <c r="E17" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F17" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D18" s="2">
+        <v>20241</v>
+      </c>
+      <c r="E18" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F18" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G18" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
+        <v>84</v>
+      </c>
+      <c r="B19" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D19" s="2">
+        <v>20189</v>
+      </c>
+      <c r="E19" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F19" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G19" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
+        <v>83</v>
+      </c>
+      <c r="B20" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C20" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D20" s="2">
+        <v>20147</v>
+      </c>
+      <c r="E20" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F20" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20087</v>
+      </c>
+      <c r="E21" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G21" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
+        <v>81</v>
+      </c>
+      <c r="B22" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C22" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D22" s="2">
+        <v>20042</v>
+      </c>
+      <c r="E22" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C23" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20003</v>
+      </c>
+      <c r="E23" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F23" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G23" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
+        <v>79</v>
+      </c>
+      <c r="B24" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D24" s="2">
+        <v>19944</v>
+      </c>
+      <c r="E24" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F24" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G24" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
+        <v>78</v>
+      </c>
+      <c r="B25" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D25" s="2">
+        <v>19892</v>
+      </c>
+      <c r="E25" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G25" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
+        <v>77</v>
+      </c>
+      <c r="B26" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D26" s="2">
+        <v>19828</v>
+      </c>
+      <c r="E26" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G26" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
+        <v>76</v>
+      </c>
+      <c r="B27" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C27" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D27" s="2">
+        <v>19779</v>
+      </c>
+      <c r="E27" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G27" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
+        <v>75</v>
+      </c>
+      <c r="B28" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C28" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D28" s="2">
+        <v>19729</v>
+      </c>
+      <c r="E28" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G28" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
+        <v>74</v>
+      </c>
+      <c r="B29" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C29" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D29" s="2">
+        <v>19673</v>
+      </c>
+      <c r="E29" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F29" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G29" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
+        <v>73</v>
+      </c>
+      <c r="B30" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C30" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D30" s="2">
+        <v>19617</v>
+      </c>
+      <c r="E30" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F30" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G30" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
+        <v>72</v>
+      </c>
+      <c r="B31" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C31" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D31" s="2">
+        <v>19574</v>
+      </c>
+      <c r="E31" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G31" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C32" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D32" s="2">
+        <v>19509</v>
+      </c>
+      <c r="E32" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F32" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G32" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C33" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D33" s="2">
+        <v>19449</v>
+      </c>
+      <c r="E33" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F33" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G33" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
+        <v>69</v>
+      </c>
+      <c r="B34" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D34" s="2">
+        <v>19401</v>
+      </c>
+      <c r="E34" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G34" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2">
+        <v>68</v>
+      </c>
+      <c r="B35" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C35" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D35" s="2">
+        <v>19343</v>
+      </c>
+      <c r="E35" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G35" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2">
+        <v>67</v>
+      </c>
+      <c r="B36" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C36" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D36" s="2">
+        <v>19281</v>
+      </c>
+      <c r="E36" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G36" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2">
+        <v>66</v>
+      </c>
+      <c r="B37" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C37" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D37" s="2">
+        <v>19216</v>
+      </c>
+      <c r="E37" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G37" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="2">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C38" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D38" s="2">
+        <v>19160</v>
+      </c>
+      <c r="E38" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G38" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2">
+        <v>64</v>
+      </c>
+      <c r="B39" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C39" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D39" s="2">
+        <v>19104</v>
+      </c>
+      <c r="E39" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2">
+        <v>63</v>
+      </c>
+      <c r="B40" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C40" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D40" s="2">
+        <v>19044</v>
+      </c>
+      <c r="E40" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F40" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G40" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2">
+        <v>62</v>
+      </c>
+      <c r="B41" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C41" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D41" s="2">
+        <v>18986</v>
+      </c>
+      <c r="E41" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G41" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2">
+        <v>61</v>
+      </c>
+      <c r="B42" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C42" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D42" s="2">
+        <v>18923</v>
+      </c>
+      <c r="E42" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G42" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
+        <v>60</v>
+      </c>
+      <c r="B43" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C43" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D43" s="2">
+        <v>18864</v>
+      </c>
+      <c r="E43" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F43" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G43" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
+        <v>59</v>
+      </c>
+      <c r="B44" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C44" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D44" s="2">
+        <v>18801</v>
+      </c>
+      <c r="E44" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F44" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G44" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C45" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D45" s="2">
+        <v>18757</v>
+      </c>
+      <c r="E45" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F45" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G45" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
+        <v>57</v>
+      </c>
+      <c r="B46" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C46" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D46" s="2">
+        <v>18686</v>
+      </c>
+      <c r="E46" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F46" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G46" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2">
+        <v>56</v>
+      </c>
+      <c r="B47" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C47" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D47" s="2">
+        <v>18615</v>
+      </c>
+      <c r="E47" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F47" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G47" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2">
+        <v>55</v>
+      </c>
+      <c r="B48" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C48" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D48" s="2">
+        <v>18552</v>
+      </c>
+      <c r="E48" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F48" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G48" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2">
+        <v>54</v>
+      </c>
+      <c r="B49" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C49" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D49" s="2">
+        <v>18484</v>
+      </c>
+      <c r="E49" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F49" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G49" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="2">
+        <v>53</v>
+      </c>
+      <c r="B50" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C50" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D50" s="2">
+        <v>18423</v>
+      </c>
+      <c r="E50" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F50" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G50" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2">
+        <v>52</v>
+      </c>
+      <c r="B51" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C51" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D51" s="2">
+        <v>18341</v>
+      </c>
+      <c r="E51" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F51" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G51" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C52" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D52" s="2">
+        <v>18271</v>
+      </c>
+      <c r="E52" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F52" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G52" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="2">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C53" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D53" s="2">
+        <v>18194</v>
+      </c>
+      <c r="E53" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F53" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G53" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2">
+        <v>49</v>
+      </c>
+      <c r="B54" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C54" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D54" s="2">
+        <v>18125</v>
+      </c>
+      <c r="E54" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F54" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G54" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="2">
+        <v>48</v>
+      </c>
+      <c r="B55" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C55" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D55" s="2">
+        <v>18066</v>
+      </c>
+      <c r="E55" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F55" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G55" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="2">
+        <v>47</v>
+      </c>
+      <c r="B56" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C56" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D56" s="2">
+        <v>17990</v>
+      </c>
+      <c r="E56" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F56" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G56" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="2">
+        <v>46</v>
+      </c>
+      <c r="B57" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C57" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D57" s="2">
+        <v>17922</v>
+      </c>
+      <c r="E57" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F57" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G57" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="2">
+        <v>45</v>
+      </c>
+      <c r="B58" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C58" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D58" s="2">
+        <v>17831</v>
+      </c>
+      <c r="E58" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F58" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G58" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="2">
+        <v>44</v>
+      </c>
+      <c r="B59" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C59" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D59" s="2">
+        <v>17751</v>
+      </c>
+      <c r="E59" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F59" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G59" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="2">
+        <v>43</v>
+      </c>
+      <c r="B60" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C60" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D60" s="2">
+        <v>17690</v>
+      </c>
+      <c r="E60" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F60" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G60" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="2">
+        <v>42</v>
+      </c>
+      <c r="B61" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C61" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D61" s="2">
+        <v>17629</v>
+      </c>
+      <c r="E61" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F61" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G61" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="2">
+        <v>41</v>
+      </c>
+      <c r="B62" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C62" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D62" s="2">
+        <v>17556</v>
+      </c>
+      <c r="E62" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F62" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G62" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="2">
+        <v>40</v>
+      </c>
+      <c r="B63" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C63" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D63" s="2">
+        <v>17470</v>
+      </c>
+      <c r="E63" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F63" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G63" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="2">
+        <v>39</v>
+      </c>
+      <c r="B64" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C64" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D64" s="2">
+        <v>17405</v>
+      </c>
+      <c r="E64" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F64" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G64" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="2">
+        <v>38</v>
+      </c>
+      <c r="B65" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C65" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D65" s="2">
+        <v>17336</v>
+      </c>
+      <c r="E65" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F65" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G65" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="2">
+        <v>37</v>
+      </c>
+      <c r="B66" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C66" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D66" s="2">
+        <v>17259</v>
+      </c>
+      <c r="E66" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F66" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G66" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="2">
+        <v>36</v>
+      </c>
+      <c r="B67" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C67" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D67" s="2">
+        <v>17183</v>
+      </c>
+      <c r="E67" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F67" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G67" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="2">
+        <v>35</v>
+      </c>
+      <c r="B68" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C68" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D68" s="2">
+        <v>17104</v>
+      </c>
+      <c r="E68" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F68" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G68" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="2">
+        <v>34</v>
+      </c>
+      <c r="B69" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C69" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D69" s="2">
+        <v>17029</v>
+      </c>
+      <c r="E69" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F69" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G69" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="2">
+        <v>33</v>
+      </c>
+      <c r="B70" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C70" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D70" s="2">
+        <v>16939</v>
+      </c>
+      <c r="E70" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F70" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G70" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="2">
+        <v>32</v>
+      </c>
+      <c r="B71" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C71" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D71" s="2">
+        <v>16864</v>
+      </c>
+      <c r="E71" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F71" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G71" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="2">
+        <v>31</v>
+      </c>
+      <c r="B72" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C72" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D72" s="2">
+        <v>16761</v>
+      </c>
+      <c r="E72" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F72" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G72" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="2">
+        <v>30</v>
+      </c>
+      <c r="B73" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C73" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D73" s="2">
+        <v>16668</v>
+      </c>
+      <c r="E73" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F73" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G73" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="2">
+        <v>29</v>
+      </c>
+      <c r="B74" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C74" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D74" s="2">
+        <v>16599</v>
+      </c>
+      <c r="E74" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F74" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G74" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="2">
+        <v>28</v>
+      </c>
+      <c r="B75" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C75" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D75" s="2">
+        <v>16505</v>
+      </c>
+      <c r="E75" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F75" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G75" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="2">
+        <v>27</v>
+      </c>
+      <c r="B76" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C76" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D76" s="2">
+        <v>16411</v>
+      </c>
+      <c r="E76" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F76" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G76" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="2">
+        <v>26</v>
+      </c>
+      <c r="B77" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C77" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D77" s="2">
+        <v>16319</v>
+      </c>
+      <c r="E77" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F77" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G77" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="2">
+        <v>25</v>
+      </c>
+      <c r="B78" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C78" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D78" s="2">
+        <v>16204</v>
+      </c>
+      <c r="E78" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F78" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G78" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="2">
+        <v>24</v>
+      </c>
+      <c r="B79" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C79" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D79" s="2">
+        <v>16106</v>
+      </c>
+      <c r="E79" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F79" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G79" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="2">
+        <v>23</v>
+      </c>
+      <c r="B80" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C80" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D80" s="2">
+        <v>16005</v>
+      </c>
+      <c r="E80" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F80" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G80" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="2">
+        <v>22</v>
+      </c>
+      <c r="B81" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C81" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D81" s="2">
+        <v>15897</v>
+      </c>
+      <c r="E81" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F81" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G81" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="2">
+        <v>21</v>
+      </c>
+      <c r="B82" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C82" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D82" s="2">
+        <v>15816</v>
+      </c>
+      <c r="E82" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F82" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G82" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="2">
+        <v>20</v>
+      </c>
+      <c r="B83" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C83" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D83" s="2">
+        <v>15711</v>
+      </c>
+      <c r="E83" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F83" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G83" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="2">
+        <v>19</v>
+      </c>
+      <c r="B84" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C84" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D84" s="2">
+        <v>15612</v>
+      </c>
+      <c r="E84" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F84" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G84" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="2">
+        <v>18</v>
+      </c>
+      <c r="B85" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C85" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D85" s="2">
+        <v>15508</v>
+      </c>
+      <c r="E85" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F85" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G85" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="2">
+        <v>17</v>
+      </c>
+      <c r="B86" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C86" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D86" s="2">
+        <v>15405</v>
+      </c>
+      <c r="E86" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F86" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G86" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="2">
+        <v>16</v>
+      </c>
+      <c r="B87" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C87" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D87" s="2">
+        <v>15309</v>
+      </c>
+      <c r="E87" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F87" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G87" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="2">
+        <v>15</v>
+      </c>
+      <c r="B88" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C88" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D88" s="2">
+        <v>15191</v>
+      </c>
+      <c r="E88" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F88" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G88" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="2">
+        <v>14</v>
+      </c>
+      <c r="B89" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C89" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D89" s="2">
+        <v>15076</v>
+      </c>
+      <c r="E89" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F89" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G89" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="2">
+        <v>13</v>
+      </c>
+      <c r="B90" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C90" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D90" s="2">
+        <v>14948</v>
+      </c>
+      <c r="E90" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F90" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G90" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="2">
+        <v>12</v>
+      </c>
+      <c r="B91" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C91" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D91" s="2">
+        <v>14837</v>
+      </c>
+      <c r="E91" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F91" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G91" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="2">
+        <v>11</v>
+      </c>
+      <c r="B92" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C92" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D92" s="2">
+        <v>14713</v>
+      </c>
+      <c r="E92" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F92" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G92" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="2">
+        <v>10</v>
+      </c>
+      <c r="B93" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C93" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D93" s="2">
+        <v>14585</v>
+      </c>
+      <c r="E93" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F93" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G93" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="2">
+        <v>9</v>
+      </c>
+      <c r="B94" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C94" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D94" s="2">
+        <v>14460</v>
+      </c>
+      <c r="E94" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F94" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G94" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="2">
+        <v>8</v>
+      </c>
+      <c r="B95" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C95" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D95" s="2">
+        <v>14328</v>
+      </c>
+      <c r="E95" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F95" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G95" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="2">
+        <v>7</v>
+      </c>
+      <c r="B96" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C96" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D96" s="2">
+        <v>14197</v>
+      </c>
+      <c r="E96" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F96" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G96" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="2">
+        <v>6</v>
+      </c>
+      <c r="B97" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C97" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D97" s="2">
+        <v>14083</v>
+      </c>
+      <c r="E97" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F97" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G97" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="2">
+        <v>5</v>
+      </c>
+      <c r="B98" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C98" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D98" s="2">
+        <v>13955</v>
+      </c>
+      <c r="E98" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F98" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G98" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="2">
+        <v>4</v>
+      </c>
+      <c r="B99" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C99" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D99" s="2">
+        <v>13830</v>
+      </c>
+      <c r="E99" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F99" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G99" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="2">
+        <v>3</v>
+      </c>
+      <c r="B100" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C100" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D100" s="2">
+        <v>13698</v>
+      </c>
+      <c r="E100" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F100" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G100" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="2">
+        <v>2</v>
+      </c>
+      <c r="B101" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C101" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D101" s="2">
+        <v>13577</v>
+      </c>
+      <c r="E101" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F101" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G101" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="2">
+        <v>1</v>
+      </c>
+      <c r="B102" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C102" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D102" s="2">
+        <v>13406</v>
+      </c>
+      <c r="E102" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F102" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G102" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="2">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C103" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D103" s="2">
+        <v>13232</v>
+      </c>
+      <c r="E103" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F103" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G103" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E575A04-79AD-E94C-AFDC-20215EB7EF7E}">
+  <dimension ref="A1:G103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>99</v>
+      </c>
+      <c r="B4" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D4" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E4" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>98</v>
+      </c>
+      <c r="B5" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C5" s="2">
+        <v>67656</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20893</v>
+      </c>
+      <c r="E5" s="2">
+        <v>59344</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10375</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>97</v>
+      </c>
+      <c r="B6" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C6" s="2">
+        <v>67645</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20891</v>
+      </c>
+      <c r="E6" s="2">
+        <v>59342</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10375</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>96</v>
+      </c>
+      <c r="B7" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C7" s="2">
+        <v>67635</v>
+      </c>
+      <c r="D7" s="2">
+        <v>20886</v>
+      </c>
+      <c r="E7" s="2">
+        <v>59337</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10375</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>95</v>
+      </c>
+      <c r="B8" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C8" s="2">
+        <v>67632</v>
+      </c>
+      <c r="D8" s="2">
+        <v>20877</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59336</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10375</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>94</v>
+      </c>
+      <c r="B9" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>67626</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20872</v>
+      </c>
+      <c r="E9" s="2">
+        <v>59330</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10370</v>
+      </c>
+      <c r="G9" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>93</v>
+      </c>
+      <c r="B10" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>67620</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20862</v>
+      </c>
+      <c r="E10" s="2">
+        <v>59323</v>
+      </c>
+      <c r="F10" s="2">
+        <v>10370</v>
+      </c>
+      <c r="G10" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>92</v>
+      </c>
+      <c r="B11" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>67612</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20847</v>
+      </c>
+      <c r="E11" s="2">
+        <v>59305</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10369</v>
+      </c>
+      <c r="G11" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>67599</v>
+      </c>
+      <c r="D12" s="2">
+        <v>20837</v>
+      </c>
+      <c r="E12" s="2">
+        <v>59299</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10368</v>
+      </c>
+      <c r="G12" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
+        <v>90</v>
+      </c>
+      <c r="B13" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C13" s="2">
+        <v>67580</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20831</v>
+      </c>
+      <c r="E13" s="2">
+        <v>59275</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10368</v>
+      </c>
+      <c r="G13" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>89</v>
+      </c>
+      <c r="B14" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>67560</v>
+      </c>
+      <c r="D14" s="2">
+        <v>20821</v>
+      </c>
+      <c r="E14" s="2">
+        <v>59259</v>
+      </c>
+      <c r="F14" s="2">
+        <v>10366</v>
+      </c>
+      <c r="G14" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
+        <v>88</v>
+      </c>
+      <c r="B15" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C15" s="2">
+        <v>67548</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20808</v>
+      </c>
+      <c r="E15" s="2">
+        <v>59247</v>
+      </c>
+      <c r="F15" s="2">
+        <v>10366</v>
+      </c>
+      <c r="G15" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C16" s="2">
+        <v>67545</v>
+      </c>
+      <c r="D16" s="2">
+        <v>20806</v>
+      </c>
+      <c r="E16" s="2">
+        <v>59245</v>
+      </c>
+      <c r="F16" s="2">
+        <v>10366</v>
+      </c>
+      <c r="G16" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2">
+        <v>86</v>
+      </c>
+      <c r="B17" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>67532</v>
+      </c>
+      <c r="D17" s="2">
+        <v>20797</v>
+      </c>
+      <c r="E17" s="2">
+        <v>59243</v>
+      </c>
+      <c r="F17" s="2">
+        <v>10366</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>67523</v>
+      </c>
+      <c r="D18" s="2">
+        <v>20791</v>
+      </c>
+      <c r="E18" s="2">
+        <v>59239</v>
+      </c>
+      <c r="F18" s="2">
+        <v>10366</v>
+      </c>
+      <c r="G18" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
+        <v>84</v>
+      </c>
+      <c r="B19" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>67509</v>
+      </c>
+      <c r="D19" s="2">
+        <v>20777</v>
+      </c>
+      <c r="E19" s="2">
+        <v>59236</v>
+      </c>
+      <c r="F19" s="2">
+        <v>10366</v>
+      </c>
+      <c r="G19" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
+        <v>83</v>
+      </c>
+      <c r="B20" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C20" s="2">
+        <v>67505</v>
+      </c>
+      <c r="D20" s="2">
+        <v>20768</v>
+      </c>
+      <c r="E20" s="2">
+        <v>59233</v>
+      </c>
+      <c r="F20" s="2">
+        <v>10364</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>67490</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20760</v>
+      </c>
+      <c r="E21" s="2">
+        <v>59228</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10364</v>
+      </c>
+      <c r="G21" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
+        <v>81</v>
+      </c>
+      <c r="B22" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C22" s="2">
+        <v>67481</v>
+      </c>
+      <c r="D22" s="2">
+        <v>20748</v>
+      </c>
+      <c r="E22" s="2">
+        <v>59223</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10364</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C23" s="2">
+        <v>67476</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20738</v>
+      </c>
+      <c r="E23" s="2">
+        <v>59220</v>
+      </c>
+      <c r="F23" s="2">
+        <v>10364</v>
+      </c>
+      <c r="G23" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
+        <v>79</v>
+      </c>
+      <c r="B24" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>67462</v>
+      </c>
+      <c r="D24" s="2">
+        <v>20727</v>
+      </c>
+      <c r="E24" s="2">
+        <v>59214</v>
+      </c>
+      <c r="F24" s="2">
+        <v>10362</v>
+      </c>
+      <c r="G24" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
+        <v>78</v>
+      </c>
+      <c r="B25" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>67436</v>
+      </c>
+      <c r="D25" s="2">
+        <v>20716</v>
+      </c>
+      <c r="E25" s="2">
+        <v>59208</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10361</v>
+      </c>
+      <c r="G25" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
+        <v>77</v>
+      </c>
+      <c r="B26" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>67421</v>
+      </c>
+      <c r="D26" s="2">
+        <v>20701</v>
+      </c>
+      <c r="E26" s="2">
+        <v>59189</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10358</v>
+      </c>
+      <c r="G26" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
+        <v>76</v>
+      </c>
+      <c r="B27" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C27" s="2">
+        <v>67410</v>
+      </c>
+      <c r="D27" s="2">
+        <v>20696</v>
+      </c>
+      <c r="E27" s="2">
+        <v>59176</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10357</v>
+      </c>
+      <c r="G27" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
+        <v>75</v>
+      </c>
+      <c r="B28" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C28" s="2">
+        <v>67399</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20686</v>
+      </c>
+      <c r="E28" s="2">
+        <v>59173</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10356</v>
+      </c>
+      <c r="G28" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
+        <v>74</v>
+      </c>
+      <c r="B29" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C29" s="2">
+        <v>67390</v>
+      </c>
+      <c r="D29" s="2">
+        <v>20683</v>
+      </c>
+      <c r="E29" s="2">
+        <v>59171</v>
+      </c>
+      <c r="F29" s="2">
+        <v>10356</v>
+      </c>
+      <c r="G29" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
+        <v>73</v>
+      </c>
+      <c r="B30" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C30" s="2">
+        <v>67367</v>
+      </c>
+      <c r="D30" s="2">
+        <v>20678</v>
+      </c>
+      <c r="E30" s="2">
+        <v>59156</v>
+      </c>
+      <c r="F30" s="2">
+        <v>10356</v>
+      </c>
+      <c r="G30" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
+        <v>72</v>
+      </c>
+      <c r="B31" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C31" s="2">
+        <v>67358</v>
+      </c>
+      <c r="D31" s="2">
+        <v>20669</v>
+      </c>
+      <c r="E31" s="2">
+        <v>59147</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10354</v>
+      </c>
+      <c r="G31" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C32" s="2">
+        <v>67342</v>
+      </c>
+      <c r="D32" s="2">
+        <v>20660</v>
+      </c>
+      <c r="E32" s="2">
+        <v>59139</v>
+      </c>
+      <c r="F32" s="2">
+        <v>10354</v>
+      </c>
+      <c r="G32" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C33" s="2">
+        <v>67325</v>
+      </c>
+      <c r="D33" s="2">
+        <v>20646</v>
+      </c>
+      <c r="E33" s="2">
+        <v>59117</v>
+      </c>
+      <c r="F33" s="2">
+        <v>10353</v>
+      </c>
+      <c r="G33" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
+        <v>69</v>
+      </c>
+      <c r="B34" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>67318</v>
+      </c>
+      <c r="D34" s="2">
+        <v>20642</v>
+      </c>
+      <c r="E34" s="2">
+        <v>59115</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10353</v>
+      </c>
+      <c r="G34" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2">
+        <v>68</v>
+      </c>
+      <c r="B35" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C35" s="2">
+        <v>67308</v>
+      </c>
+      <c r="D35" s="2">
+        <v>20640</v>
+      </c>
+      <c r="E35" s="2">
+        <v>59111</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10353</v>
+      </c>
+      <c r="G35" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2">
+        <v>67</v>
+      </c>
+      <c r="B36" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C36" s="2">
+        <v>67295</v>
+      </c>
+      <c r="D36" s="2">
+        <v>20624</v>
+      </c>
+      <c r="E36" s="2">
+        <v>59108</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10352</v>
+      </c>
+      <c r="G36" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2">
+        <v>66</v>
+      </c>
+      <c r="B37" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C37" s="2">
+        <v>67291</v>
+      </c>
+      <c r="D37" s="2">
+        <v>20617</v>
+      </c>
+      <c r="E37" s="2">
+        <v>59108</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10352</v>
+      </c>
+      <c r="G37" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="2">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C38" s="2">
+        <v>67274</v>
+      </c>
+      <c r="D38" s="2">
+        <v>20600</v>
+      </c>
+      <c r="E38" s="2">
+        <v>59102</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10350</v>
+      </c>
+      <c r="G38" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2">
+        <v>64</v>
+      </c>
+      <c r="B39" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C39" s="2">
+        <v>67269</v>
+      </c>
+      <c r="D39" s="2">
+        <v>20587</v>
+      </c>
+      <c r="E39" s="2">
+        <v>59093</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10349</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2">
+        <v>63</v>
+      </c>
+      <c r="B40" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C40" s="2">
+        <v>67261</v>
+      </c>
+      <c r="D40" s="2">
+        <v>20573</v>
+      </c>
+      <c r="E40" s="2">
+        <v>59091</v>
+      </c>
+      <c r="F40" s="2">
+        <v>10349</v>
+      </c>
+      <c r="G40" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2">
+        <v>62</v>
+      </c>
+      <c r="B41" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C41" s="2">
+        <v>67244</v>
+      </c>
+      <c r="D41" s="2">
+        <v>20564</v>
+      </c>
+      <c r="E41" s="2">
+        <v>59086</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10349</v>
+      </c>
+      <c r="G41" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2">
+        <v>61</v>
+      </c>
+      <c r="B42" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C42" s="2">
+        <v>67219</v>
+      </c>
+      <c r="D42" s="2">
+        <v>20550</v>
+      </c>
+      <c r="E42" s="2">
+        <v>59075</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10348</v>
+      </c>
+      <c r="G42" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
+        <v>60</v>
+      </c>
+      <c r="B43" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C43" s="2">
+        <v>67206</v>
+      </c>
+      <c r="D43" s="2">
+        <v>20539</v>
+      </c>
+      <c r="E43" s="2">
+        <v>59066</v>
+      </c>
+      <c r="F43" s="2">
+        <v>10347</v>
+      </c>
+      <c r="G43" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
+        <v>59</v>
+      </c>
+      <c r="B44" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C44" s="2">
+        <v>67190</v>
+      </c>
+      <c r="D44" s="2">
+        <v>20521</v>
+      </c>
+      <c r="E44" s="2">
+        <v>59037</v>
+      </c>
+      <c r="F44" s="2">
+        <v>10345</v>
+      </c>
+      <c r="G44" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C45" s="2">
+        <v>67172</v>
+      </c>
+      <c r="D45" s="2">
+        <v>20504</v>
+      </c>
+      <c r="E45" s="2">
+        <v>59012</v>
+      </c>
+      <c r="F45" s="2">
+        <v>10344</v>
+      </c>
+      <c r="G45" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
+        <v>57</v>
+      </c>
+      <c r="B46" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C46" s="2">
+        <v>67155</v>
+      </c>
+      <c r="D46" s="2">
+        <v>20489</v>
+      </c>
+      <c r="E46" s="2">
+        <v>59008</v>
+      </c>
+      <c r="F46" s="2">
+        <v>10342</v>
+      </c>
+      <c r="G46" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2">
+        <v>56</v>
+      </c>
+      <c r="B47" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C47" s="2">
+        <v>67142</v>
+      </c>
+      <c r="D47" s="2">
+        <v>20476</v>
+      </c>
+      <c r="E47" s="2">
+        <v>59003</v>
+      </c>
+      <c r="F47" s="2">
+        <v>10339</v>
+      </c>
+      <c r="G47" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2">
+        <v>55</v>
+      </c>
+      <c r="B48" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C48" s="2">
+        <v>67123</v>
+      </c>
+      <c r="D48" s="2">
+        <v>20463</v>
+      </c>
+      <c r="E48" s="2">
+        <v>58994</v>
+      </c>
+      <c r="F48" s="2">
+        <v>10338</v>
+      </c>
+      <c r="G48" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2">
+        <v>54</v>
+      </c>
+      <c r="B49" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C49" s="2">
+        <v>67100</v>
+      </c>
+      <c r="D49" s="2">
+        <v>20445</v>
+      </c>
+      <c r="E49" s="2">
+        <v>58976</v>
+      </c>
+      <c r="F49" s="2">
+        <v>10335</v>
+      </c>
+      <c r="G49" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="2">
+        <v>53</v>
+      </c>
+      <c r="B50" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C50" s="2">
+        <v>67077</v>
+      </c>
+      <c r="D50" s="2">
+        <v>20424</v>
+      </c>
+      <c r="E50" s="2">
+        <v>58958</v>
+      </c>
+      <c r="F50" s="2">
+        <v>10329</v>
+      </c>
+      <c r="G50" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2">
+        <v>52</v>
+      </c>
+      <c r="B51" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C51" s="2">
+        <v>67059</v>
+      </c>
+      <c r="D51" s="2">
+        <v>20417</v>
+      </c>
+      <c r="E51" s="2">
+        <v>58945</v>
+      </c>
+      <c r="F51" s="2">
+        <v>10327</v>
+      </c>
+      <c r="G51" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C52" s="2">
+        <v>67047</v>
+      </c>
+      <c r="D52" s="2">
+        <v>20403</v>
+      </c>
+      <c r="E52" s="2">
+        <v>58938</v>
+      </c>
+      <c r="F52" s="2">
+        <v>10326</v>
+      </c>
+      <c r="G52" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="2">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C53" s="2">
+        <v>67029</v>
+      </c>
+      <c r="D53" s="2">
+        <v>20396</v>
+      </c>
+      <c r="E53" s="2">
+        <v>58934</v>
+      </c>
+      <c r="F53" s="2">
+        <v>10325</v>
+      </c>
+      <c r="G53" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2">
+        <v>49</v>
+      </c>
+      <c r="B54" s="2">
+        <v>15999</v>
+      </c>
+      <c r="C54" s="2">
+        <v>67016</v>
+      </c>
+      <c r="D54" s="2">
+        <v>20387</v>
+      </c>
+      <c r="E54" s="2">
+        <v>58931</v>
+      </c>
+      <c r="F54" s="2">
+        <v>10325</v>
+      </c>
+      <c r="G54" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="2">
+        <v>48</v>
+      </c>
+      <c r="B55" s="2">
+        <v>15998</v>
+      </c>
+      <c r="C55" s="2">
+        <v>66987</v>
+      </c>
+      <c r="D55" s="2">
+        <v>20366</v>
+      </c>
+      <c r="E55" s="2">
+        <v>58916</v>
+      </c>
+      <c r="F55" s="2">
+        <v>10324</v>
+      </c>
+      <c r="G55" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="2">
+        <v>47</v>
+      </c>
+      <c r="B56" s="2">
+        <v>15997</v>
+      </c>
+      <c r="C56" s="2">
+        <v>66972</v>
+      </c>
+      <c r="D56" s="2">
+        <v>20353</v>
+      </c>
+      <c r="E56" s="2">
+        <v>58908</v>
+      </c>
+      <c r="F56" s="2">
+        <v>10324</v>
+      </c>
+      <c r="G56" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="2">
+        <v>46</v>
+      </c>
+      <c r="B57" s="2">
+        <v>15994</v>
+      </c>
+      <c r="C57" s="2">
+        <v>66956</v>
+      </c>
+      <c r="D57" s="2">
+        <v>20340</v>
+      </c>
+      <c r="E57" s="2">
+        <v>58899</v>
+      </c>
+      <c r="F57" s="2">
+        <v>10322</v>
+      </c>
+      <c r="G57" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="2">
+        <v>45</v>
+      </c>
+      <c r="B58" s="2">
+        <v>15989</v>
+      </c>
+      <c r="C58" s="2">
+        <v>66939</v>
+      </c>
+      <c r="D58" s="2">
+        <v>20325</v>
+      </c>
+      <c r="E58" s="2">
+        <v>58886</v>
+      </c>
+      <c r="F58" s="2">
+        <v>10320</v>
+      </c>
+      <c r="G58" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="2">
+        <v>44</v>
+      </c>
+      <c r="B59" s="2">
+        <v>15986</v>
+      </c>
+      <c r="C59" s="2">
+        <v>66925</v>
+      </c>
+      <c r="D59" s="2">
+        <v>20316</v>
+      </c>
+      <c r="E59" s="2">
+        <v>58873</v>
+      </c>
+      <c r="F59" s="2">
+        <v>10315</v>
+      </c>
+      <c r="G59" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="2">
+        <v>43</v>
+      </c>
+      <c r="B60" s="2">
+        <v>15981</v>
+      </c>
+      <c r="C60" s="2">
+        <v>66885</v>
+      </c>
+      <c r="D60" s="2">
+        <v>20281</v>
+      </c>
+      <c r="E60" s="2">
+        <v>58862</v>
+      </c>
+      <c r="F60" s="2">
+        <v>10315</v>
+      </c>
+      <c r="G60" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="2">
+        <v>42</v>
+      </c>
+      <c r="B61" s="2">
+        <v>15977</v>
+      </c>
+      <c r="C61" s="2">
+        <v>66878</v>
+      </c>
+      <c r="D61" s="2">
+        <v>20271</v>
+      </c>
+      <c r="E61" s="2">
+        <v>58858</v>
+      </c>
+      <c r="F61" s="2">
+        <v>10313</v>
+      </c>
+      <c r="G61" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="2">
+        <v>41</v>
+      </c>
+      <c r="B62" s="2">
+        <v>15975</v>
+      </c>
+      <c r="C62" s="2">
+        <v>66869</v>
+      </c>
+      <c r="D62" s="2">
+        <v>20260</v>
+      </c>
+      <c r="E62" s="2">
+        <v>58848</v>
+      </c>
+      <c r="F62" s="2">
+        <v>10311</v>
+      </c>
+      <c r="G62" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="2">
+        <v>40</v>
+      </c>
+      <c r="B63" s="2">
+        <v>15967</v>
+      </c>
+      <c r="C63" s="2">
+        <v>66856</v>
+      </c>
+      <c r="D63" s="2">
+        <v>20255</v>
+      </c>
+      <c r="E63" s="2">
+        <v>58840</v>
+      </c>
+      <c r="F63" s="2">
+        <v>10308</v>
+      </c>
+      <c r="G63" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="2">
+        <v>39</v>
+      </c>
+      <c r="B64" s="2">
+        <v>15966</v>
+      </c>
+      <c r="C64" s="2">
+        <v>66840</v>
+      </c>
+      <c r="D64" s="2">
+        <v>20240</v>
+      </c>
+      <c r="E64" s="2">
+        <v>58825</v>
+      </c>
+      <c r="F64" s="2">
+        <v>10305</v>
+      </c>
+      <c r="G64" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="2">
+        <v>38</v>
+      </c>
+      <c r="B65" s="2">
+        <v>15960</v>
+      </c>
+      <c r="C65" s="2">
+        <v>66826</v>
+      </c>
+      <c r="D65" s="2">
+        <v>20219</v>
+      </c>
+      <c r="E65" s="2">
+        <v>58812</v>
+      </c>
+      <c r="F65" s="2">
+        <v>10301</v>
+      </c>
+      <c r="G65" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="2">
+        <v>37</v>
+      </c>
+      <c r="B66" s="2">
+        <v>15956</v>
+      </c>
+      <c r="C66" s="2">
+        <v>66799</v>
+      </c>
+      <c r="D66" s="2">
+        <v>20208</v>
+      </c>
+      <c r="E66" s="2">
+        <v>58793</v>
+      </c>
+      <c r="F66" s="2">
+        <v>10298</v>
+      </c>
+      <c r="G66" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="2">
+        <v>36</v>
+      </c>
+      <c r="B67" s="2">
+        <v>15945</v>
+      </c>
+      <c r="C67" s="2">
+        <v>66755</v>
+      </c>
+      <c r="D67" s="2">
+        <v>20201</v>
+      </c>
+      <c r="E67" s="2">
+        <v>58773</v>
+      </c>
+      <c r="F67" s="2">
+        <v>10293</v>
+      </c>
+      <c r="G67" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="2">
+        <v>35</v>
+      </c>
+      <c r="B68" s="2">
+        <v>15941</v>
+      </c>
+      <c r="C68" s="2">
+        <v>66739</v>
+      </c>
+      <c r="D68" s="2">
+        <v>20185</v>
+      </c>
+      <c r="E68" s="2">
+        <v>58762</v>
+      </c>
+      <c r="F68" s="2">
+        <v>10290</v>
+      </c>
+      <c r="G68" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="2">
+        <v>34</v>
+      </c>
+      <c r="B69" s="2">
+        <v>15933</v>
+      </c>
+      <c r="C69" s="2">
+        <v>66716</v>
+      </c>
+      <c r="D69" s="2">
+        <v>20166</v>
+      </c>
+      <c r="E69" s="2">
+        <v>58752</v>
+      </c>
+      <c r="F69" s="2">
+        <v>10288</v>
+      </c>
+      <c r="G69" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="2">
+        <v>33</v>
+      </c>
+      <c r="B70" s="2">
+        <v>15920</v>
+      </c>
+      <c r="C70" s="2">
+        <v>66690</v>
+      </c>
+      <c r="D70" s="2">
+        <v>20149</v>
+      </c>
+      <c r="E70" s="2">
+        <v>58728</v>
+      </c>
+      <c r="F70" s="2">
+        <v>10288</v>
+      </c>
+      <c r="G70" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="2">
+        <v>32</v>
+      </c>
+      <c r="B71" s="2">
+        <v>15909</v>
+      </c>
+      <c r="C71" s="2">
+        <v>66662</v>
+      </c>
+      <c r="D71" s="2">
+        <v>20115</v>
+      </c>
+      <c r="E71" s="2">
+        <v>58675</v>
+      </c>
+      <c r="F71" s="2">
+        <v>10286</v>
+      </c>
+      <c r="G71" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="2">
+        <v>31</v>
+      </c>
+      <c r="B72" s="2">
+        <v>15898</v>
+      </c>
+      <c r="C72" s="2">
+        <v>66627</v>
+      </c>
+      <c r="D72" s="2">
+        <v>20075</v>
+      </c>
+      <c r="E72" s="2">
+        <v>58648</v>
+      </c>
+      <c r="F72" s="2">
+        <v>10274</v>
+      </c>
+      <c r="G72" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="2">
+        <v>30</v>
+      </c>
+      <c r="B73" s="2">
+        <v>15888</v>
+      </c>
+      <c r="C73" s="2">
+        <v>66572</v>
+      </c>
+      <c r="D73" s="2">
+        <v>20016</v>
+      </c>
+      <c r="E73" s="2">
+        <v>58576</v>
+      </c>
+      <c r="F73" s="2">
+        <v>10262</v>
+      </c>
+      <c r="G73" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="2">
+        <v>29</v>
+      </c>
+      <c r="B74" s="2">
+        <v>15872</v>
+      </c>
+      <c r="C74" s="2">
+        <v>66507</v>
+      </c>
+      <c r="D74" s="2">
+        <v>19979</v>
+      </c>
+      <c r="E74" s="2">
+        <v>58524</v>
+      </c>
+      <c r="F74" s="2">
+        <v>10256</v>
+      </c>
+      <c r="G74" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="2">
+        <v>28</v>
+      </c>
+      <c r="B75" s="2">
+        <v>15854</v>
+      </c>
+      <c r="C75" s="2">
+        <v>66471</v>
+      </c>
+      <c r="D75" s="2">
+        <v>19954</v>
+      </c>
+      <c r="E75" s="2">
+        <v>58477</v>
+      </c>
+      <c r="F75" s="2">
+        <v>10248</v>
+      </c>
+      <c r="G75" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="2">
+        <v>27</v>
+      </c>
+      <c r="B76" s="2">
+        <v>15836</v>
+      </c>
+      <c r="C76" s="2">
+        <v>66405</v>
+      </c>
+      <c r="D76" s="2">
+        <v>19917</v>
+      </c>
+      <c r="E76" s="2">
+        <v>58444</v>
+      </c>
+      <c r="F76" s="2">
+        <v>10238</v>
+      </c>
+      <c r="G76" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="2">
+        <v>26</v>
+      </c>
+      <c r="B77" s="2">
+        <v>15817</v>
+      </c>
+      <c r="C77" s="2">
+        <v>66337</v>
+      </c>
+      <c r="D77" s="2">
+        <v>19871</v>
+      </c>
+      <c r="E77" s="2">
+        <v>58395</v>
+      </c>
+      <c r="F77" s="2">
+        <v>10234</v>
+      </c>
+      <c r="G77" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="2">
+        <v>25</v>
+      </c>
+      <c r="B78" s="2">
+        <v>15800</v>
+      </c>
+      <c r="C78" s="2">
+        <v>66261</v>
+      </c>
+      <c r="D78" s="2">
+        <v>19817</v>
+      </c>
+      <c r="E78" s="2">
+        <v>58316</v>
+      </c>
+      <c r="F78" s="2">
+        <v>10220</v>
+      </c>
+      <c r="G78" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="2">
+        <v>24</v>
+      </c>
+      <c r="B79" s="2">
+        <v>15778</v>
+      </c>
+      <c r="C79" s="2">
+        <v>66174</v>
+      </c>
+      <c r="D79" s="2">
+        <v>19777</v>
+      </c>
+      <c r="E79" s="2">
+        <v>58242</v>
+      </c>
+      <c r="F79" s="2">
+        <v>10204</v>
+      </c>
+      <c r="G79" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="2">
+        <v>23</v>
+      </c>
+      <c r="B80" s="2">
+        <v>15758</v>
+      </c>
+      <c r="C80" s="2">
+        <v>66058</v>
+      </c>
+      <c r="D80" s="2">
+        <v>19719</v>
+      </c>
+      <c r="E80" s="2">
+        <v>58168</v>
+      </c>
+      <c r="F80" s="2">
+        <v>10199</v>
+      </c>
+      <c r="G80" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="2">
+        <v>22</v>
+      </c>
+      <c r="B81" s="2">
+        <v>15732</v>
+      </c>
+      <c r="C81" s="2">
+        <v>65998</v>
+      </c>
+      <c r="D81" s="2">
+        <v>19676</v>
+      </c>
+      <c r="E81" s="2">
+        <v>58075</v>
+      </c>
+      <c r="F81" s="2">
+        <v>10183</v>
+      </c>
+      <c r="G81" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="2">
+        <v>21</v>
+      </c>
+      <c r="B82" s="2">
+        <v>15706</v>
+      </c>
+      <c r="C82" s="2">
+        <v>65931</v>
+      </c>
+      <c r="D82" s="2">
+        <v>19616</v>
+      </c>
+      <c r="E82" s="2">
+        <v>58013</v>
+      </c>
+      <c r="F82" s="2">
+        <v>10166</v>
+      </c>
+      <c r="G82" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="2">
+        <v>20</v>
+      </c>
+      <c r="B83" s="2">
+        <v>15683</v>
+      </c>
+      <c r="C83" s="2">
+        <v>65833</v>
+      </c>
+      <c r="D83" s="2">
+        <v>19543</v>
+      </c>
+      <c r="E83" s="2">
+        <v>57925</v>
+      </c>
+      <c r="F83" s="2">
+        <v>10147</v>
+      </c>
+      <c r="G83" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="2">
+        <v>19</v>
+      </c>
+      <c r="B84" s="2">
+        <v>15651</v>
+      </c>
+      <c r="C84" s="2">
+        <v>65701</v>
+      </c>
+      <c r="D84" s="2">
+        <v>19485</v>
+      </c>
+      <c r="E84" s="2">
+        <v>57802</v>
+      </c>
+      <c r="F84" s="2">
+        <v>10126</v>
+      </c>
+      <c r="G84" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="2">
+        <v>18</v>
+      </c>
+      <c r="B85" s="2">
+        <v>15619</v>
+      </c>
+      <c r="C85" s="2">
+        <v>65553</v>
+      </c>
+      <c r="D85" s="2">
+        <v>19416</v>
+      </c>
+      <c r="E85" s="2">
+        <v>57689</v>
+      </c>
+      <c r="F85" s="2">
+        <v>10106</v>
+      </c>
+      <c r="G85" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="2">
+        <v>17</v>
+      </c>
+      <c r="B86" s="2">
+        <v>15576</v>
+      </c>
+      <c r="C86" s="2">
+        <v>65403</v>
+      </c>
+      <c r="D86" s="2">
+        <v>19323</v>
+      </c>
+      <c r="E86" s="2">
+        <v>57480</v>
+      </c>
+      <c r="F86" s="2">
+        <v>10073</v>
+      </c>
+      <c r="G86" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="2">
+        <v>16</v>
+      </c>
+      <c r="B87" s="2">
+        <v>15547</v>
+      </c>
+      <c r="C87" s="2">
+        <v>65310</v>
+      </c>
+      <c r="D87" s="2">
+        <v>19233</v>
+      </c>
+      <c r="E87" s="2">
+        <v>57383</v>
+      </c>
+      <c r="F87" s="2">
+        <v>10054</v>
+      </c>
+      <c r="G87" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="2">
+        <v>15</v>
+      </c>
+      <c r="B88" s="2">
+        <v>15505</v>
+      </c>
+      <c r="C88" s="2">
+        <v>65209</v>
+      </c>
+      <c r="D88" s="2">
+        <v>19130</v>
+      </c>
+      <c r="E88" s="2">
+        <v>57281</v>
+      </c>
+      <c r="F88" s="2">
+        <v>10035</v>
+      </c>
+      <c r="G88" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="2">
+        <v>14</v>
+      </c>
+      <c r="B89" s="2">
+        <v>15463</v>
+      </c>
+      <c r="C89" s="2">
+        <v>65095</v>
+      </c>
+      <c r="D89" s="2">
+        <v>19052</v>
+      </c>
+      <c r="E89" s="2">
+        <v>57154</v>
+      </c>
+      <c r="F89" s="2">
+        <v>10021</v>
+      </c>
+      <c r="G89" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="2">
+        <v>13</v>
+      </c>
+      <c r="B90" s="2">
+        <v>15438</v>
+      </c>
+      <c r="C90" s="2">
+        <v>64957</v>
+      </c>
+      <c r="D90" s="2">
+        <v>18968</v>
+      </c>
+      <c r="E90" s="2">
+        <v>57059</v>
+      </c>
+      <c r="F90" s="2">
+        <v>10001</v>
+      </c>
+      <c r="G90" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="2">
+        <v>12</v>
+      </c>
+      <c r="B91" s="2">
+        <v>15402</v>
+      </c>
+      <c r="C91" s="2">
+        <v>64845</v>
+      </c>
+      <c r="D91" s="2">
+        <v>18862</v>
+      </c>
+      <c r="E91" s="2">
+        <v>56905</v>
+      </c>
+      <c r="F91" s="2">
+        <v>9975</v>
+      </c>
+      <c r="G91" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="2">
+        <v>11</v>
+      </c>
+      <c r="B92" s="2">
+        <v>15380</v>
+      </c>
+      <c r="C92" s="2">
+        <v>64726</v>
+      </c>
+      <c r="D92" s="2">
+        <v>18784</v>
+      </c>
+      <c r="E92" s="2">
+        <v>56821</v>
+      </c>
+      <c r="F92" s="2">
+        <v>9960</v>
+      </c>
+      <c r="G92" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="2">
+        <v>10</v>
+      </c>
+      <c r="B93" s="2">
+        <v>15340</v>
+      </c>
+      <c r="C93" s="2">
+        <v>64578</v>
+      </c>
+      <c r="D93" s="2">
+        <v>18694</v>
+      </c>
+      <c r="E93" s="2">
+        <v>56679</v>
+      </c>
+      <c r="F93" s="2">
+        <v>9934</v>
+      </c>
+      <c r="G93" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="2">
+        <v>9</v>
+      </c>
+      <c r="B94" s="2">
+        <v>15314</v>
+      </c>
+      <c r="C94" s="2">
+        <v>64482</v>
+      </c>
+      <c r="D94" s="2">
+        <v>18611</v>
+      </c>
+      <c r="E94" s="2">
+        <v>56592</v>
+      </c>
+      <c r="F94" s="2">
+        <v>9928</v>
+      </c>
+      <c r="G94" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="2">
+        <v>8</v>
+      </c>
+      <c r="B95" s="2">
+        <v>15282</v>
+      </c>
+      <c r="C95" s="2">
+        <v>64387</v>
+      </c>
+      <c r="D95" s="2">
+        <v>18514</v>
+      </c>
+      <c r="E95" s="2">
+        <v>56483</v>
+      </c>
+      <c r="F95" s="2">
+        <v>9913</v>
+      </c>
+      <c r="G95" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="2">
+        <v>7</v>
+      </c>
+      <c r="B96" s="2">
+        <v>15257</v>
+      </c>
+      <c r="C96" s="2">
+        <v>64288</v>
+      </c>
+      <c r="D96" s="2">
+        <v>18408</v>
+      </c>
+      <c r="E96" s="2">
+        <v>56384</v>
+      </c>
+      <c r="F96" s="2">
+        <v>9902</v>
+      </c>
+      <c r="G96" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="2">
+        <v>6</v>
+      </c>
+      <c r="B97" s="2">
+        <v>15235</v>
+      </c>
+      <c r="C97" s="2">
+        <v>64217</v>
+      </c>
+      <c r="D97" s="2">
+        <v>18318</v>
+      </c>
+      <c r="E97" s="2">
+        <v>56325</v>
+      </c>
+      <c r="F97" s="2">
+        <v>9888</v>
+      </c>
+      <c r="G97" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="2">
+        <v>5</v>
+      </c>
+      <c r="B98" s="2">
+        <v>15213</v>
+      </c>
+      <c r="C98" s="2">
+        <v>64103</v>
+      </c>
+      <c r="D98" s="2">
+        <v>18176</v>
+      </c>
+      <c r="E98" s="2">
+        <v>56242</v>
+      </c>
+      <c r="F98" s="2">
+        <v>9869</v>
+      </c>
+      <c r="G98" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="2">
+        <v>4</v>
+      </c>
+      <c r="B99" s="2">
+        <v>15182</v>
+      </c>
+      <c r="C99" s="2">
+        <v>63988</v>
+      </c>
+      <c r="D99" s="2">
+        <v>18061</v>
+      </c>
+      <c r="E99" s="2">
+        <v>56135</v>
+      </c>
+      <c r="F99" s="2">
+        <v>9862</v>
+      </c>
+      <c r="G99" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="2">
+        <v>3</v>
+      </c>
+      <c r="B100" s="2">
+        <v>15166</v>
+      </c>
+      <c r="C100" s="2">
+        <v>63859</v>
+      </c>
+      <c r="D100" s="2">
+        <v>17915</v>
+      </c>
+      <c r="E100" s="2">
+        <v>55999</v>
+      </c>
+      <c r="F100" s="2">
+        <v>9855</v>
+      </c>
+      <c r="G100" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="2">
+        <v>2</v>
+      </c>
+      <c r="B101" s="2">
+        <v>15154</v>
+      </c>
+      <c r="C101" s="2">
+        <v>63724</v>
+      </c>
+      <c r="D101" s="2">
+        <v>17714</v>
+      </c>
+      <c r="E101" s="2">
+        <v>55859</v>
+      </c>
+      <c r="F101" s="2">
+        <v>9847</v>
+      </c>
+      <c r="G101" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="2">
+        <v>1</v>
+      </c>
+      <c r="B102" s="2">
+        <v>15128</v>
+      </c>
+      <c r="C102" s="2">
+        <v>63545</v>
+      </c>
+      <c r="D102" s="2">
+        <v>17395</v>
+      </c>
+      <c r="E102" s="2">
+        <v>55639</v>
+      </c>
+      <c r="F102" s="2">
+        <v>9821</v>
+      </c>
+      <c r="G102" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="2">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2">
+        <v>15096</v>
+      </c>
+      <c r="C103" s="2">
+        <v>63325</v>
+      </c>
+      <c r="D103" s="2">
+        <v>16982</v>
+      </c>
+      <c r="E103" s="2">
+        <v>55349</v>
+      </c>
+      <c r="F103" s="2">
+        <v>9782</v>
+      </c>
+      <c r="G103" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FACF50B5-34EA-8C43-868E-52F4160D1DF2}">
+  <dimension ref="A1:G103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>99</v>
+      </c>
+      <c r="B4" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D4" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E4" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>98</v>
+      </c>
+      <c r="B5" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C5" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20896</v>
+      </c>
+      <c r="E5" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>97</v>
+      </c>
+      <c r="B6" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C6" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20889</v>
+      </c>
+      <c r="E6" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>96</v>
+      </c>
+      <c r="B7" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C7" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D7" s="2">
+        <v>20877</v>
+      </c>
+      <c r="E7" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>95</v>
+      </c>
+      <c r="B8" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C8" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D8" s="2">
+        <v>20870</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>94</v>
+      </c>
+      <c r="B9" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20857</v>
+      </c>
+      <c r="E9" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G9" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>93</v>
+      </c>
+      <c r="B10" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20850</v>
+      </c>
+      <c r="E10" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F10" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G10" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>92</v>
+      </c>
+      <c r="B11" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20840</v>
+      </c>
+      <c r="E11" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G11" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D12" s="2">
+        <v>20830</v>
+      </c>
+      <c r="E12" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G12" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
+        <v>90</v>
+      </c>
+      <c r="B13" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C13" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20822</v>
+      </c>
+      <c r="E13" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G13" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>89</v>
+      </c>
+      <c r="B14" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D14" s="2">
+        <v>20806</v>
+      </c>
+      <c r="E14" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F14" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G14" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
+        <v>88</v>
+      </c>
+      <c r="B15" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C15" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20800</v>
+      </c>
+      <c r="E15" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F15" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G15" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C16" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D16" s="2">
+        <v>20788</v>
+      </c>
+      <c r="E16" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F16" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G16" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2">
+        <v>86</v>
+      </c>
+      <c r="B17" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D17" s="2">
+        <v>20777</v>
+      </c>
+      <c r="E17" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F17" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D18" s="2">
+        <v>20768</v>
+      </c>
+      <c r="E18" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F18" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G18" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
+        <v>84</v>
+      </c>
+      <c r="B19" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D19" s="2">
+        <v>20757</v>
+      </c>
+      <c r="E19" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F19" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G19" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
+        <v>83</v>
+      </c>
+      <c r="B20" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C20" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D20" s="2">
+        <v>20743</v>
+      </c>
+      <c r="E20" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F20" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20728</v>
+      </c>
+      <c r="E21" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G21" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
+        <v>81</v>
+      </c>
+      <c r="B22" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C22" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D22" s="2">
+        <v>20714</v>
+      </c>
+      <c r="E22" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C23" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20709</v>
+      </c>
+      <c r="E23" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F23" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G23" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
+        <v>79</v>
+      </c>
+      <c r="B24" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D24" s="2">
+        <v>20696</v>
+      </c>
+      <c r="E24" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F24" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G24" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
+        <v>78</v>
+      </c>
+      <c r="B25" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D25" s="2">
+        <v>20681</v>
+      </c>
+      <c r="E25" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G25" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
+        <v>77</v>
+      </c>
+      <c r="B26" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D26" s="2">
+        <v>20664</v>
+      </c>
+      <c r="E26" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G26" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
+        <v>76</v>
+      </c>
+      <c r="B27" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C27" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D27" s="2">
+        <v>20646</v>
+      </c>
+      <c r="E27" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G27" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
+        <v>75</v>
+      </c>
+      <c r="B28" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C28" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20633</v>
+      </c>
+      <c r="E28" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G28" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
+        <v>74</v>
+      </c>
+      <c r="B29" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C29" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D29" s="2">
+        <v>20617</v>
+      </c>
+      <c r="E29" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F29" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G29" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
+        <v>73</v>
+      </c>
+      <c r="B30" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C30" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D30" s="2">
+        <v>20604</v>
+      </c>
+      <c r="E30" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F30" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G30" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
+        <v>72</v>
+      </c>
+      <c r="B31" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C31" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D31" s="2">
+        <v>20592</v>
+      </c>
+      <c r="E31" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G31" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C32" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D32" s="2">
+        <v>20582</v>
+      </c>
+      <c r="E32" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F32" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G32" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C33" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D33" s="2">
+        <v>20568</v>
+      </c>
+      <c r="E33" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F33" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G33" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
+        <v>69</v>
+      </c>
+      <c r="B34" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D34" s="2">
+        <v>20558</v>
+      </c>
+      <c r="E34" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G34" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2">
+        <v>68</v>
+      </c>
+      <c r="B35" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C35" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D35" s="2">
+        <v>20549</v>
+      </c>
+      <c r="E35" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G35" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2">
+        <v>67</v>
+      </c>
+      <c r="B36" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C36" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D36" s="2">
+        <v>20533</v>
+      </c>
+      <c r="E36" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G36" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2">
+        <v>66</v>
+      </c>
+      <c r="B37" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C37" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D37" s="2">
+        <v>20517</v>
+      </c>
+      <c r="E37" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G37" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="2">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C38" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D38" s="2">
+        <v>20507</v>
+      </c>
+      <c r="E38" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G38" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2">
+        <v>64</v>
+      </c>
+      <c r="B39" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C39" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D39" s="2">
+        <v>20489</v>
+      </c>
+      <c r="E39" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2">
+        <v>63</v>
+      </c>
+      <c r="B40" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C40" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D40" s="2">
+        <v>20467</v>
+      </c>
+      <c r="E40" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F40" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G40" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2">
+        <v>62</v>
+      </c>
+      <c r="B41" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C41" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D41" s="2">
+        <v>20451</v>
+      </c>
+      <c r="E41" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G41" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2">
+        <v>61</v>
+      </c>
+      <c r="B42" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C42" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D42" s="2">
+        <v>20431</v>
+      </c>
+      <c r="E42" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G42" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
+        <v>60</v>
+      </c>
+      <c r="B43" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C43" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D43" s="2">
+        <v>20412</v>
+      </c>
+      <c r="E43" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F43" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G43" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
+        <v>59</v>
+      </c>
+      <c r="B44" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C44" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D44" s="2">
+        <v>20396</v>
+      </c>
+      <c r="E44" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F44" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G44" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C45" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D45" s="2">
+        <v>20373</v>
+      </c>
+      <c r="E45" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F45" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G45" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
+        <v>57</v>
+      </c>
+      <c r="B46" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C46" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D46" s="2">
+        <v>20360</v>
+      </c>
+      <c r="E46" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F46" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G46" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2">
+        <v>56</v>
+      </c>
+      <c r="B47" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C47" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D47" s="2">
+        <v>20342</v>
+      </c>
+      <c r="E47" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F47" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G47" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2">
+        <v>55</v>
+      </c>
+      <c r="B48" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C48" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D48" s="2">
+        <v>20316</v>
+      </c>
+      <c r="E48" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F48" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G48" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2">
+        <v>54</v>
+      </c>
+      <c r="B49" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C49" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D49" s="2">
+        <v>20300</v>
+      </c>
+      <c r="E49" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F49" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G49" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="2">
+        <v>53</v>
+      </c>
+      <c r="B50" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C50" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D50" s="2">
+        <v>20280</v>
+      </c>
+      <c r="E50" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F50" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G50" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2">
+        <v>52</v>
+      </c>
+      <c r="B51" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C51" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D51" s="2">
+        <v>20257</v>
+      </c>
+      <c r="E51" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F51" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G51" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C52" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D52" s="2">
+        <v>20238</v>
+      </c>
+      <c r="E52" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F52" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G52" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="2">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C53" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D53" s="2">
+        <v>20226</v>
+      </c>
+      <c r="E53" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F53" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G53" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2">
+        <v>49</v>
+      </c>
+      <c r="B54" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C54" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D54" s="2">
+        <v>20207</v>
+      </c>
+      <c r="E54" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F54" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G54" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="2">
+        <v>48</v>
+      </c>
+      <c r="B55" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C55" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D55" s="2">
+        <v>20183</v>
+      </c>
+      <c r="E55" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F55" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G55" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="2">
+        <v>47</v>
+      </c>
+      <c r="B56" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C56" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D56" s="2">
+        <v>20162</v>
+      </c>
+      <c r="E56" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F56" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G56" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="2">
+        <v>46</v>
+      </c>
+      <c r="B57" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C57" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D57" s="2">
+        <v>20149</v>
+      </c>
+      <c r="E57" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F57" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G57" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="2">
+        <v>45</v>
+      </c>
+      <c r="B58" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C58" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D58" s="2">
+        <v>20126</v>
+      </c>
+      <c r="E58" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F58" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G58" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="2">
+        <v>44</v>
+      </c>
+      <c r="B59" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C59" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D59" s="2">
+        <v>20105</v>
+      </c>
+      <c r="E59" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F59" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G59" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="2">
+        <v>43</v>
+      </c>
+      <c r="B60" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C60" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D60" s="2">
+        <v>20081</v>
+      </c>
+      <c r="E60" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F60" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G60" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="2">
+        <v>42</v>
+      </c>
+      <c r="B61" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C61" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D61" s="2">
+        <v>20054</v>
+      </c>
+      <c r="E61" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F61" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G61" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="2">
+        <v>41</v>
+      </c>
+      <c r="B62" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C62" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D62" s="2">
+        <v>20028</v>
+      </c>
+      <c r="E62" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F62" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G62" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="2">
+        <v>40</v>
+      </c>
+      <c r="B63" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C63" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D63" s="2">
+        <v>20009</v>
+      </c>
+      <c r="E63" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F63" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G63" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="2">
+        <v>39</v>
+      </c>
+      <c r="B64" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C64" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D64" s="2">
+        <v>19992</v>
+      </c>
+      <c r="E64" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F64" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G64" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="2">
+        <v>38</v>
+      </c>
+      <c r="B65" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C65" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D65" s="2">
+        <v>19964</v>
+      </c>
+      <c r="E65" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F65" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G65" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="2">
+        <v>37</v>
+      </c>
+      <c r="B66" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C66" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D66" s="2">
+        <v>19938</v>
+      </c>
+      <c r="E66" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F66" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G66" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="2">
+        <v>36</v>
+      </c>
+      <c r="B67" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C67" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D67" s="2">
+        <v>19918</v>
+      </c>
+      <c r="E67" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F67" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G67" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="2">
+        <v>35</v>
+      </c>
+      <c r="B68" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C68" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D68" s="2">
+        <v>19895</v>
+      </c>
+      <c r="E68" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F68" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G68" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="2">
+        <v>34</v>
+      </c>
+      <c r="B69" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C69" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D69" s="2">
+        <v>19858</v>
+      </c>
+      <c r="E69" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F69" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G69" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="2">
+        <v>33</v>
+      </c>
+      <c r="B70" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C70" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D70" s="2">
+        <v>19827</v>
+      </c>
+      <c r="E70" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F70" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G70" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="2">
+        <v>32</v>
+      </c>
+      <c r="B71" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C71" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D71" s="2">
+        <v>19787</v>
+      </c>
+      <c r="E71" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F71" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G71" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="2">
+        <v>31</v>
+      </c>
+      <c r="B72" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C72" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D72" s="2">
+        <v>19752</v>
+      </c>
+      <c r="E72" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F72" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G72" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="2">
+        <v>30</v>
+      </c>
+      <c r="B73" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C73" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D73" s="2">
+        <v>19729</v>
+      </c>
+      <c r="E73" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F73" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G73" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="2">
+        <v>29</v>
+      </c>
+      <c r="B74" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C74" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D74" s="2">
+        <v>19686</v>
+      </c>
+      <c r="E74" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F74" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G74" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="2">
+        <v>28</v>
+      </c>
+      <c r="B75" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C75" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D75" s="2">
+        <v>19644</v>
+      </c>
+      <c r="E75" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F75" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G75" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="2">
+        <v>27</v>
+      </c>
+      <c r="B76" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C76" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D76" s="2">
+        <v>19601</v>
+      </c>
+      <c r="E76" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F76" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G76" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="2">
+        <v>26</v>
+      </c>
+      <c r="B77" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C77" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D77" s="2">
+        <v>19565</v>
+      </c>
+      <c r="E77" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F77" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G77" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="2">
+        <v>25</v>
+      </c>
+      <c r="B78" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C78" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D78" s="2">
+        <v>19522</v>
+      </c>
+      <c r="E78" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F78" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G78" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="2">
+        <v>24</v>
+      </c>
+      <c r="B79" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C79" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D79" s="2">
+        <v>19486</v>
+      </c>
+      <c r="E79" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F79" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G79" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="2">
+        <v>23</v>
+      </c>
+      <c r="B80" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C80" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D80" s="2">
+        <v>19449</v>
+      </c>
+      <c r="E80" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F80" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G80" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="2">
+        <v>22</v>
+      </c>
+      <c r="B81" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C81" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D81" s="2">
+        <v>19416</v>
+      </c>
+      <c r="E81" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F81" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G81" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="2">
+        <v>21</v>
+      </c>
+      <c r="B82" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C82" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D82" s="2">
+        <v>19371</v>
+      </c>
+      <c r="E82" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F82" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G82" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="2">
+        <v>20</v>
+      </c>
+      <c r="B83" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C83" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D83" s="2">
+        <v>19312</v>
+      </c>
+      <c r="E83" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F83" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G83" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="2">
+        <v>19</v>
+      </c>
+      <c r="B84" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C84" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D84" s="2">
+        <v>19264</v>
+      </c>
+      <c r="E84" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F84" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G84" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="2">
+        <v>18</v>
+      </c>
+      <c r="B85" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C85" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D85" s="2">
+        <v>19201</v>
+      </c>
+      <c r="E85" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F85" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G85" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="2">
+        <v>17</v>
+      </c>
+      <c r="B86" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C86" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D86" s="2">
+        <v>19156</v>
+      </c>
+      <c r="E86" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F86" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G86" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="2">
+        <v>16</v>
+      </c>
+      <c r="B87" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C87" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D87" s="2">
+        <v>19078</v>
+      </c>
+      <c r="E87" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F87" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G87" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="2">
+        <v>15</v>
+      </c>
+      <c r="B88" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C88" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D88" s="2">
+        <v>19028</v>
+      </c>
+      <c r="E88" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F88" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G88" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="2">
+        <v>14</v>
+      </c>
+      <c r="B89" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C89" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D89" s="2">
+        <v>18947</v>
+      </c>
+      <c r="E89" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F89" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G89" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="2">
+        <v>13</v>
+      </c>
+      <c r="B90" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C90" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D90" s="2">
+        <v>18868</v>
+      </c>
+      <c r="E90" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F90" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G90" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="2">
+        <v>12</v>
+      </c>
+      <c r="B91" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C91" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D91" s="2">
+        <v>18801</v>
+      </c>
+      <c r="E91" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F91" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G91" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="2">
+        <v>11</v>
+      </c>
+      <c r="B92" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C92" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D92" s="2">
+        <v>18678</v>
+      </c>
+      <c r="E92" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F92" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G92" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="2">
+        <v>10</v>
+      </c>
+      <c r="B93" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C93" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D93" s="2">
+        <v>18594</v>
+      </c>
+      <c r="E93" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F93" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G93" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="2">
+        <v>9</v>
+      </c>
+      <c r="B94" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C94" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D94" s="2">
+        <v>18479</v>
+      </c>
+      <c r="E94" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F94" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G94" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="2">
+        <v>8</v>
+      </c>
+      <c r="B95" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C95" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D95" s="2">
+        <v>18337</v>
+      </c>
+      <c r="E95" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F95" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G95" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="2">
+        <v>7</v>
+      </c>
+      <c r="B96" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C96" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D96" s="2">
+        <v>18208</v>
+      </c>
+      <c r="E96" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F96" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G96" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="2">
+        <v>6</v>
+      </c>
+      <c r="B97" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C97" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D97" s="2">
+        <v>18034</v>
+      </c>
+      <c r="E97" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F97" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G97" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="2">
+        <v>5</v>
+      </c>
+      <c r="B98" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C98" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D98" s="2">
+        <v>17872</v>
+      </c>
+      <c r="E98" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F98" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G98" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="2">
+        <v>4</v>
+      </c>
+      <c r="B99" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C99" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D99" s="2">
+        <v>17684</v>
+      </c>
+      <c r="E99" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F99" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G99" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="2">
+        <v>3</v>
+      </c>
+      <c r="B100" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C100" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D100" s="2">
+        <v>17468</v>
+      </c>
+      <c r="E100" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F100" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G100" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="2">
+        <v>2</v>
+      </c>
+      <c r="B101" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C101" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D101" s="2">
+        <v>17249</v>
+      </c>
+      <c r="E101" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F101" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G101" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="2">
+        <v>1</v>
+      </c>
+      <c r="B102" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C102" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D102" s="2">
+        <v>16991</v>
+      </c>
+      <c r="E102" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F102" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G102" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="2">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C103" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D103" s="2">
+        <v>16739</v>
+      </c>
+      <c r="E103" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F103" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G103" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1589813E-03CA-874D-AD95-996D6C25389B}">
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>-50</v>
+      </c>
+      <c r="B4" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D4" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E4" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>-49</v>
+      </c>
+      <c r="B5" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C5" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E5" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>-48</v>
+      </c>
+      <c r="B6" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C6" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E6" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>-47</v>
+      </c>
+      <c r="B7" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C7" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D7" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E7" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>-46</v>
+      </c>
+      <c r="B8" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C8" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D8" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>-45</v>
+      </c>
+      <c r="B9" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20905</v>
+      </c>
+      <c r="E9" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G9" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>-44</v>
+      </c>
+      <c r="B10" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20868</v>
+      </c>
+      <c r="E10" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F10" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G10" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>-43</v>
+      </c>
+      <c r="B11" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20839</v>
+      </c>
+      <c r="E11" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G11" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>-42</v>
+      </c>
+      <c r="B12" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D12" s="2">
+        <v>20791</v>
+      </c>
+      <c r="E12" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G12" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
+        <v>-41</v>
+      </c>
+      <c r="B13" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C13" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20744</v>
+      </c>
+      <c r="E13" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G13" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>-40</v>
+      </c>
+      <c r="B14" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D14" s="2">
+        <v>20708</v>
+      </c>
+      <c r="E14" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F14" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G14" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
+        <v>-39</v>
+      </c>
+      <c r="B15" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C15" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20671</v>
+      </c>
+      <c r="E15" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F15" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G15" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>-38</v>
+      </c>
+      <c r="B16" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C16" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D16" s="2">
+        <v>20616</v>
+      </c>
+      <c r="E16" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F16" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G16" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2">
+        <v>-37</v>
+      </c>
+      <c r="B17" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D17" s="2">
+        <v>20574</v>
+      </c>
+      <c r="E17" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F17" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
+        <v>-36</v>
+      </c>
+      <c r="B18" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D18" s="2">
+        <v>20532</v>
+      </c>
+      <c r="E18" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F18" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G18" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
+        <v>-35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D19" s="2">
+        <v>20499</v>
+      </c>
+      <c r="E19" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F19" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G19" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
+        <v>-34</v>
+      </c>
+      <c r="B20" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C20" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D20" s="2">
+        <v>20478</v>
+      </c>
+      <c r="E20" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F20" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2">
+        <v>-33</v>
+      </c>
+      <c r="B21" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20441</v>
+      </c>
+      <c r="E21" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G21" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
+        <v>-32</v>
+      </c>
+      <c r="B22" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C22" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D22" s="2">
+        <v>20402</v>
+      </c>
+      <c r="E22" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
+        <v>-31</v>
+      </c>
+      <c r="B23" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C23" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20365</v>
+      </c>
+      <c r="E23" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F23" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G23" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
+        <v>-30</v>
+      </c>
+      <c r="B24" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D24" s="2">
+        <v>20309</v>
+      </c>
+      <c r="E24" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F24" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G24" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
+        <v>-29</v>
+      </c>
+      <c r="B25" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D25" s="2">
+        <v>20256</v>
+      </c>
+      <c r="E25" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G25" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
+        <v>-28</v>
+      </c>
+      <c r="B26" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D26" s="2">
+        <v>20199</v>
+      </c>
+      <c r="E26" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G26" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
+        <v>-27</v>
+      </c>
+      <c r="B27" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C27" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D27" s="2">
+        <v>20123</v>
+      </c>
+      <c r="E27" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G27" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
+        <v>-26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C28" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20055</v>
+      </c>
+      <c r="E28" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G28" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
+        <v>-25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C29" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D29" s="2">
+        <v>20003</v>
+      </c>
+      <c r="E29" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F29" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G29" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
+        <v>-24</v>
+      </c>
+      <c r="B30" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C30" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D30" s="2">
+        <v>19918</v>
+      </c>
+      <c r="E30" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F30" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G30" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
+        <v>-23</v>
+      </c>
+      <c r="B31" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C31" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D31" s="2">
+        <v>19834</v>
+      </c>
+      <c r="E31" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G31" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
+        <v>-22</v>
+      </c>
+      <c r="B32" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C32" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D32" s="2">
+        <v>19712</v>
+      </c>
+      <c r="E32" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F32" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G32" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
+        <v>-21</v>
+      </c>
+      <c r="B33" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C33" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D33" s="2">
+        <v>19578</v>
+      </c>
+      <c r="E33" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F33" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G33" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
+        <v>-20</v>
+      </c>
+      <c r="B34" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D34" s="2">
+        <v>19445</v>
+      </c>
+      <c r="E34" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G34" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2">
+        <v>-19</v>
+      </c>
+      <c r="B35" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C35" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D35" s="2">
+        <v>19234</v>
+      </c>
+      <c r="E35" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G35" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2">
+        <v>-18</v>
+      </c>
+      <c r="B36" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C36" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D36" s="2">
+        <v>19009</v>
+      </c>
+      <c r="E36" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G36" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2">
+        <v>-17</v>
+      </c>
+      <c r="B37" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C37" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D37" s="2">
+        <v>18727</v>
+      </c>
+      <c r="E37" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G37" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="2">
+        <v>-16</v>
+      </c>
+      <c r="B38" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C38" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D38" s="2">
+        <v>18444</v>
+      </c>
+      <c r="E38" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G38" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2">
+        <v>-15</v>
+      </c>
+      <c r="B39" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C39" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D39" s="2">
+        <v>18114</v>
+      </c>
+      <c r="E39" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2">
+        <v>-14</v>
+      </c>
+      <c r="B40" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C40" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D40" s="2">
+        <v>17801</v>
+      </c>
+      <c r="E40" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F40" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G40" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2">
+        <v>-13</v>
+      </c>
+      <c r="B41" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C41" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D41" s="2">
+        <v>17524</v>
+      </c>
+      <c r="E41" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G41" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2">
+        <v>-12</v>
+      </c>
+      <c r="B42" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C42" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D42" s="2">
+        <v>17252</v>
+      </c>
+      <c r="E42" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G42" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
+        <v>-11</v>
+      </c>
+      <c r="B43" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C43" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D43" s="2">
+        <v>17098</v>
+      </c>
+      <c r="E43" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F43" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G43" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
+        <v>-10</v>
+      </c>
+      <c r="B44" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C44" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D44" s="2">
+        <v>16989</v>
+      </c>
+      <c r="E44" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F44" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G44" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2">
+        <v>-9</v>
+      </c>
+      <c r="B45" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C45" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D45" s="2">
+        <v>16918</v>
+      </c>
+      <c r="E45" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F45" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G45" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
+        <v>-8</v>
+      </c>
+      <c r="B46" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C46" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D46" s="2">
+        <v>16837</v>
+      </c>
+      <c r="E46" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F46" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G46" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2">
+        <v>-7</v>
+      </c>
+      <c r="B47" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C47" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D47" s="2">
+        <v>16761</v>
+      </c>
+      <c r="E47" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F47" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G47" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2">
+        <v>-6</v>
+      </c>
+      <c r="B48" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C48" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D48" s="2">
+        <v>16702</v>
+      </c>
+      <c r="E48" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F48" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G48" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2">
+        <v>-5</v>
+      </c>
+      <c r="B49" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C49" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D49" s="2">
+        <v>16641</v>
+      </c>
+      <c r="E49" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F49" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G49" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="2">
+        <v>-4</v>
+      </c>
+      <c r="B50" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C50" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D50" s="2">
+        <v>16605</v>
+      </c>
+      <c r="E50" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F50" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G50" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2">
+        <v>-3</v>
+      </c>
+      <c r="B51" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C51" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D51" s="2">
+        <v>16564</v>
+      </c>
+      <c r="E51" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F51" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G51" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2">
+        <v>-2</v>
+      </c>
+      <c r="B52" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C52" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D52" s="2">
+        <v>16520</v>
+      </c>
+      <c r="E52" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F52" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G52" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B53" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C53" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D53" s="2">
+        <v>16513</v>
+      </c>
+      <c r="E53" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F53" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G53" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2">
+        <v>16001</v>
+      </c>
+      <c r="C54" s="2">
+        <v>67679</v>
+      </c>
+      <c r="D54" s="2">
+        <v>16506</v>
+      </c>
+      <c r="E54" s="2">
+        <v>59354</v>
+      </c>
+      <c r="F54" s="2">
+        <v>10377</v>
+      </c>
+      <c r="G54" s="2">
+        <v>7424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF314745-0037-1945-B2C1-1732C0AB8B8E}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -4622,7 +12998,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4646,7 +13022,7 @@
         <v>97</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="56">
@@ -4657,7 +13033,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="70" customHeight="1">
@@ -4668,7 +13044,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="70">
@@ -4676,10 +13052,10 @@
         <v>94</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="70">
@@ -4687,21 +13063,21 @@
         <v>95</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="56">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="42">
       <c r="A10" s="17" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
